--- a/artfynd/A 42668-2025 artfynd.xlsx
+++ b/artfynd/A 42668-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>67730429</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410313.8012161446</v>
+        <v>410314</v>
       </c>
       <c r="R2" t="n">
-        <v>6603198.804418665</v>
+        <v>6603199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2017-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,12 +791,7 @@
         <v>92673277</v>
       </c>
       <c r="B3" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410347.2541077902</v>
+        <v>410347</v>
       </c>
       <c r="R3" t="n">
-        <v>6603068.197620333</v>
+        <v>6603068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +868,9 @@
           <t>2021-04-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
